--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-25.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-25.xlsx
@@ -930,12 +930,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,12 +952,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1398,26 +1398,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1428,22 +1424,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,18 +1686,18 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,26 +1772,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,26 +1832,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1862,15 +1858,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2860,22 +2860,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2890,22 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2976,18 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3002,26 +3006,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3036,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3066,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3092,26 +3092,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3282,10 +3282,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3300,12 +3304,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3322,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3344,14 +3348,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,18 +3532,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3558,12 +3562,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3573,11 +3577,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,22 +3592,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,18 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3674,22 +3678,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,26 +3708,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4010,22 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4040,26 +4040,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4100,26 +4100,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -4130,22 +4130,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4160,22 +4160,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4556,16 +4556,24 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -4578,26 +4586,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4608,26 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4668,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4698,26 +4694,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4728,26 +4720,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4758,20 +4742,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4784,18 +4764,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4806,16 +4794,20 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4828,12 +4820,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4850,22 +4842,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4876,22 +4872,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4902,26 +4902,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,18 +4962,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -4984,24 +4992,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,17 +5014,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5044,26 +5044,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5240,22 +5240,26 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -5266,22 +5270,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -5292,26 +5300,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -5322,26 +5326,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
@@ -5538,22 +5538,18 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
           <t>$159.9B</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208">
@@ -5564,12 +5560,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -5586,18 +5582,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>$159.9B</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -5758,18 +5758,18 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218">
@@ -5780,18 +5780,18 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -6150,15 +6150,19 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
         <v>3</v>
@@ -6172,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,18 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6216,22 +6224,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6242,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6286,18 +6290,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -6308,22 +6316,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6334,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6356,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6378,19 +6382,15 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>3</v>
@@ -6534,22 +6534,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6564,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6594,26 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6624,22 +6624,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6650,26 +6654,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6684,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6714,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6870,22 +6870,18 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -6900,18 +6896,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>4.140%</t>
+          <t>4.211%</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4.211%</t>
+          <t>4.140%</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7178,18 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,26 +7204,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -7264,22 +7260,26 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7790,22 +7790,18 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
@@ -7816,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7834,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,12 +7860,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7886,18 +7882,22 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,22 +7930,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8324,22 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8354,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -8524,7 +8524,11 @@
           <t>0.9%</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8542,26 +8546,14 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr"/>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,26 +8564,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -8602,26 +8594,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8632,22 +8624,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,26 +8684,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8718,26 +8714,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8748,22 +8744,18 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8778,12 +8770,20 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F335" t="n">
         <v>2</v>
       </c>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,26 +9768,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F376" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="377">
@@ -9798,18 +9794,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9824,22 +9820,26 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -9850,18 +9850,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,18 +9902,22 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -9924,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9946,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9968,22 +9972,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -9994,19 +9998,15 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10064,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,18 +10086,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -10196,26 +10196,22 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -10226,22 +10222,22 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F395" t="n">
@@ -10256,26 +10252,26 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
@@ -10286,26 +10282,26 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
@@ -10316,22 +10312,26 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr"/>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -10536,22 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409">
@@ -10562,26 +10562,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -10592,26 +10592,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -10622,26 +10618,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -10652,22 +10648,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10682,22 +10678,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10712,26 +10708,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -10742,22 +10738,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10768,26 +10768,26 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
           <t>4.1%</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -10798,22 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10904,26 +10904,26 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -10934,18 +10934,18 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,22 +10960,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10990,22 +10990,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11020,18 +11020,18 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,26 +11046,26 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,14 +11510,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -12360,18 +12360,22 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F490" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="491">
@@ -12382,18 +12386,22 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12404,7 +12412,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -12430,14 +12438,14 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F493" t="n">
@@ -12452,18 +12460,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -12474,7 +12482,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -12500,18 +12508,18 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
@@ -12522,22 +12530,18 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F497" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -12548,22 +12552,18 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -13262,18 +13262,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -13302,14 +13298,18 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="536">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13446,14 +13446,14 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr"/>
       <c r="F543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="544">
@@ -13464,7 +13464,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -13500,14 +13500,14 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr"/>
       <c r="F546" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="547">
@@ -13522,8 +13522,16 @@
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
-      <c r="D547" t="inlineStr"/>
-      <c r="E547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>1.47M</t>
+        </is>
+      </c>
       <c r="F547" t="n">
         <v>1</v>
       </c>
@@ -13536,14 +13544,18 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr"/>
-      <c r="E548" t="inlineStr"/>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-9.0%</t>
+        </is>
+      </c>
       <c r="F548" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="549">
@@ -13576,14 +13588,22 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
-      <c r="E550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>1.35M</t>
+        </is>
+      </c>
       <c r="F550" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551">
@@ -13950,22 +13970,14 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D569" t="inlineStr"/>
+      <c r="E569" t="inlineStr"/>
       <c r="F569" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="570">
@@ -13976,12 +13988,20 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
-      <c r="D570" t="inlineStr"/>
-      <c r="E570" t="inlineStr"/>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F570" t="n">
         <v>2</v>
       </c>
@@ -14110,7 +14130,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -14128,14 +14148,22 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F578" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="579">
@@ -14216,7 +14244,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
@@ -14270,7 +14298,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
@@ -14288,7 +14316,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
@@ -14448,7 +14476,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
@@ -14484,7 +14512,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
@@ -14502,7 +14530,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14556,14 +14584,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14574,14 +14602,14 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -14592,7 +14620,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -14610,7 +14638,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
@@ -14628,7 +14656,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14646,7 +14674,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
@@ -14700,7 +14728,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14880,7 +14908,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14898,7 +14926,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15236,18 +15264,18 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F636" t="n">
@@ -15314,18 +15342,18 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F639" t="n">
@@ -15440,18 +15468,18 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -15466,18 +15494,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F645" t="n">
@@ -15808,7 +15836,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15826,7 +15854,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -16050,7 +16078,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16068,7 +16096,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16086,7 +16114,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -16122,14 +16150,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="680">
@@ -16140,7 +16168,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -16158,14 +16186,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -16194,7 +16222,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-25.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-25.xlsx
@@ -930,12 +930,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,12 +952,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,15 +1686,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1712,26 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1772,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,18 +1832,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2860,22 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -2886,26 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3006,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3036,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3066,22 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3092,18 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3122,18 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,14 +3282,10 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3304,12 +3300,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3326,12 +3322,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,10 +3344,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,26 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -3562,26 +3562,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3592,18 +3588,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,22 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3663,11 +3663,11 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3678,22 +3678,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3708,18 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4010,22 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,26 +4070,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4100,22 +4100,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4130,26 +4130,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4160,22 +4160,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4556,24 +4556,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -4586,18 +4578,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -4608,26 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4668,22 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4694,22 +4698,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4720,12 +4728,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -4742,16 +4750,20 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4764,26 +4776,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4794,20 +4798,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4820,18 +4820,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4842,26 +4850,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4872,26 +4876,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4902,26 +4902,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4962,26 +4962,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4992,16 +4984,24 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5074,26 +5074,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5240,26 +5240,22 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -5270,26 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -5300,22 +5292,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -5326,22 +5322,26 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5560,18 +5560,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>$159.9B</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -5582,22 +5586,18 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
           <t>$159.9B</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -5758,12 +5758,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5780,18 +5780,18 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -5802,18 +5802,18 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
@@ -6150,19 +6150,15 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
         <v>3</v>
@@ -6176,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,22 +6194,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6224,18 +6216,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6246,12 +6242,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6264,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,22 +6286,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6316,18 +6308,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6338,12 +6334,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,15 +6356,19 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>3</v>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6534,26 +6534,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6594,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6624,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -6654,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6684,22 +6680,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6714,22 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6870,18 +6870,22 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -6896,22 +6900,18 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>4.211%</t>
+          <t>4.140%</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4.140%</t>
+          <t>4.211%</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7178,18 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,22 +7204,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -7260,26 +7264,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7790,12 +7790,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -7812,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7834,22 +7834,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7882,22 +7882,18 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -7908,12 +7904,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,22 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7956,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,18 +7974,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8324,18 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8350,22 +8354,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,26 +8516,26 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -8546,12 +8546,20 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F327" t="n">
         <v>2</v>
       </c>
@@ -8564,22 +8572,18 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8594,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8624,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8654,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8684,26 +8688,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -8714,26 +8718,14 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8744,7 +8736,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -8752,7 +8744,11 @@
           <t>0.9%</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8770,22 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,18 +9794,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9820,26 +9820,22 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -9850,18 +9846,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -9876,22 +9872,26 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -9902,22 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -9928,12 +9924,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,12 +9946,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,19 +9968,15 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
         <v>3</v>
@@ -9998,18 +9990,22 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -10020,12 +10016,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,12 +10038,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,18 +10060,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10086,22 +10086,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -10196,22 +10196,26 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr"/>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -10222,26 +10226,22 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -10252,22 +10252,22 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -10282,26 +10282,26 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -10312,26 +10312,26 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
@@ -10536,22 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10562,26 +10562,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
           <t>4.1%</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -10592,22 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10618,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -10648,22 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10678,22 +10682,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10708,26 +10712,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10742,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10768,26 +10768,26 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10798,22 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10904,26 +10904,26 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -10934,18 +10934,18 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,22 +10960,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10990,22 +10990,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11020,18 +11020,18 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,26 +11046,26 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -11474,14 +11474,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
@@ -12360,22 +12360,18 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F490" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -12386,22 +12382,18 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F491" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492">
@@ -12412,7 +12404,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -12438,18 +12430,18 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -12460,18 +12452,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -12482,7 +12474,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -12508,18 +12500,22 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -12530,18 +12526,22 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F497" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="498">
@@ -12552,14 +12552,14 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F498" t="n">
@@ -13280,14 +13280,18 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535">
@@ -13298,18 +13302,14 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13428,14 +13428,14 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -13500,14 +13500,14 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr"/>
       <c r="F546" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="547">
@@ -13988,22 +13988,14 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E570" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D570" t="inlineStr"/>
+      <c r="E570" t="inlineStr"/>
       <c r="F570" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="571">
@@ -14130,7 +14122,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -14148,18 +14140,18 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F578" t="n">
@@ -14244,14 +14236,22 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F582" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="583">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
@@ -14512,7 +14512,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
@@ -14656,7 +14656,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14908,7 +14908,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15264,18 +15264,18 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F636" t="n">
@@ -15342,18 +15342,18 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F639" t="n">
@@ -15468,18 +15468,18 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -15494,18 +15494,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F645" t="n">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16114,7 +16114,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
